--- a/StraddleDart_rev7/Build_Guide_rev7.xlsx
+++ b/StraddleDart_rev7/Build_Guide_rev7.xlsx
@@ -535,7 +535,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="23.85" customHeight="1" s="20">
       <c r="A4" s="23" t="inlineStr">
         <is>
@@ -1492,7 +1491,7 @@
     <row r="59" ht="15" customHeight="1" s="20">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>48. Armrest pad and grip: bend the 1-1/8 in 316 stick and weld it to its 316 base plate; bolt the plate through the console top and the inner rail (4 x 1/4 316, crush tubes, Tef-Gel and a gasket; never weld stainless to the aluminium rail); fit the ball knob; set the armrest height (drv_armrest_h) and reach (drv_reach) to the driver</t>
+          <t>48. Armrest pad and grip: bend the 1-1/8 in 316 stick and weld it to its 316 base plate; bolt the plate through the console top and the inner rail (4 x 1/4 316, crush tubes, Tef-Gel and a gasket; never weld stainless to the aluminium rail); turn an M16 x 1.5 stud with a square shoulder on the stick end, run a 316 M16 x 1.5 nylon-insert lock nut onto it, thread on the Hurst T-handle (no adapter) across the boat and tighten the lock nut up hard under its neck, then cross-pin handle and stud with a 1/4 in 316 pin 0.4 in above the shoulder; set the armrest height (drv_armrest_h) and reach (drv_reach) to the driver</t>
         </is>
       </c>
       <c r="B59" s="29" t="n">
@@ -1503,7 +1502,7 @@
       </c>
       <c r="D59" s="28" t="inlineStr">
         <is>
-          <t>Hand lands on the knob seated against the backrest, forearm on the pad</t>
+          <t>Hand lands on the T-handle seated against the backrest, forearm on the pad</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1686,6 @@
         </is>
       </c>
     </row>
-    <row r="70"/>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
@@ -1722,7 +1720,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="36" t="inlineStr">
         <is>
